--- a/AAII_Financials/Quarterly/RWEOY_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/RWEOY_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="424" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="445" uniqueCount="92">
   <si>
     <t>RWEOY</t>
   </si>
@@ -656,164 +656,167 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AP102"/>
+  <dimension ref="A5:AQ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="10.140625" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="22" width="16" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="42" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="43" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="23" width="16" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="43" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="44" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:43" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:43" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43465</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43373</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43190</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43100</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>43008</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42916</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42825</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42735</v>
       </c>
-      <c r="AP7" s="2">
+      <c r="AQ7" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
@@ -856,86 +859,89 @@
       <c r="P8" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="Q8" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R8" s="3">
         <v>12664300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>11671600</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>9026900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>8677800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>12269800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>5209100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>3958000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>4980000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>4284800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>3027600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2914900</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>4148700</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>4690700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2623900</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>3205700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>4445100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>4369600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>3350500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>3296200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>4046100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>3904500</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>3293000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>3504000</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>5028600</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>13997700</v>
       </c>
-      <c r="AP8" s="3">
+      <c r="AQ8" s="3">
         <v>10549000</v>
       </c>
     </row>
-    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
@@ -978,86 +984,89 @@
       <c r="P9" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="Q9" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R9" s="3">
         <v>4286400</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>12755500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>8930000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>8213500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>8151300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>4237700</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>2928500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>3768600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>4540200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1676200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1726900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>2251600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>2347700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1896300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>2939800</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>3189100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>3025900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>2628300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>2809800</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>2753800</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>2897000</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>2447100</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>2564900</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>3498000</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>10903500</v>
       </c>
-      <c r="AP9" s="3">
+      <c r="AQ9" s="3">
         <v>8321100</v>
       </c>
     </row>
-    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
@@ -1100,86 +1109,89 @@
       <c r="P10" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="Q10" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R10" s="3">
         <v>8377900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>-1083900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>96800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>464400</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>4118500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>971400</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>1029400</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>1211400</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>-255300</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>1351300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>1188000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>1897100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>2343000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>727600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>265900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>1256000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>1343800</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>722200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>486400</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>1292300</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>1007500</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>846000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>939100</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>1530600</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>3094200</v>
       </c>
-      <c r="AP10" s="3">
+      <c r="AQ10" s="3">
         <v>2227900</v>
       </c>
     </row>
-    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1222,8 +1234,9 @@
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
       <c r="AP11" s="3"/>
+      <c r="AQ11" s="3"/>
     </row>
-    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1344,8 +1357,11 @@
       <c r="AP12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1466,8 +1482,11 @@
       <c r="AP13" s="3">
         <v>0</v>
       </c>
+      <c r="AQ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1510,8 +1529,8 @@
       <c r="P14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q14" s="3">
-        <v>0</v>
+      <c r="Q14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R14" s="3">
         <v>0</v>
@@ -1540,8 +1559,8 @@
       <c r="Z14" s="3">
         <v>0</v>
       </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
+      <c r="AA14" s="3">
+        <v>0</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
@@ -1558,38 +1577,41 @@
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH14" s="3">
         <v>55600</v>
       </c>
-      <c r="AH14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AI14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AJ14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AK14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL14" s="3">
         <v>80800</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>2200</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>337700</v>
       </c>
-      <c r="AN14" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AO14" s="3" t="s">
         <v>8</v>
       </c>
       <c r="AP14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:43" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1632,86 +1654,89 @@
       <c r="P15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q15" s="3">
+      <c r="Q15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R15" s="3">
         <v>644600</v>
       </c>
-      <c r="R15" s="3">
+      <c r="S15" s="3">
         <v>492800</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>438500</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>414500</v>
       </c>
-      <c r="U15" s="3">
+      <c r="V15" s="3">
         <v>543100</v>
       </c>
-      <c r="V15" s="3">
+      <c r="W15" s="3">
         <v>392400</v>
       </c>
-      <c r="W15" s="3">
+      <c r="X15" s="3">
         <v>1220900</v>
       </c>
-      <c r="X15" s="3">
+      <c r="Y15" s="3">
         <v>376600</v>
       </c>
-      <c r="Y15" s="3">
+      <c r="Z15" s="3">
         <v>2008800</v>
       </c>
-      <c r="Z15" s="3">
+      <c r="AA15" s="3">
         <v>402700</v>
       </c>
-      <c r="AA15" s="3">
+      <c r="AB15" s="3">
         <v>411300</v>
       </c>
-      <c r="AB15" s="3">
+      <c r="AC15" s="3">
         <v>390500</v>
       </c>
-      <c r="AC15" s="3">
+      <c r="AD15" s="3">
         <v>2423500</v>
       </c>
-      <c r="AD15" s="3">
+      <c r="AE15" s="3">
         <v>706800</v>
       </c>
-      <c r="AE15" s="3">
+      <c r="AF15" s="3">
         <v>304700</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>303800</v>
       </c>
-      <c r="AG15" s="3">
+      <c r="AH15" s="3">
         <v>592600</v>
       </c>
-      <c r="AH15" s="3">
+      <c r="AI15" s="3">
         <v>259200</v>
       </c>
-      <c r="AI15" s="3">
+      <c r="AJ15" s="3">
         <v>251400</v>
       </c>
-      <c r="AJ15" s="3">
+      <c r="AK15" s="3">
         <v>230600</v>
       </c>
-      <c r="AK15" s="3">
+      <c r="AL15" s="3">
         <v>967200</v>
       </c>
-      <c r="AL15" s="3">
+      <c r="AM15" s="3">
         <v>1348600</v>
       </c>
-      <c r="AM15" s="3">
+      <c r="AN15" s="3">
         <v>1171400</v>
       </c>
-      <c r="AN15" s="3">
+      <c r="AO15" s="3">
         <v>304000</v>
       </c>
-      <c r="AO15" s="3">
+      <c r="AP15" s="3">
         <v>5561500</v>
       </c>
-      <c r="AP15" s="3">
+      <c r="AQ15" s="3">
         <v>679600</v>
       </c>
     </row>
-    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:43" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1751,8 +1776,9 @@
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
       <c r="AP16" s="3"/>
+      <c r="AQ16" s="3"/>
     </row>
-    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
@@ -1795,86 +1821,89 @@
       <c r="P17" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="Q17" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R17" s="3">
         <v>14940400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>12181700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>9799400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>5575800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>14354600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>3049600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>3317900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>4514500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>4956100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2520000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2584400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2751300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>4608900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2882400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>3750400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>3893600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>4141300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>3454600</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>3542100</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>3591600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>4027900</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>3326700</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1837800</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>4304400</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>20440700</v>
       </c>
-      <c r="AP17" s="3">
+      <c r="AQ17" s="3">
         <v>10675800</v>
       </c>
     </row>
-    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
@@ -1917,86 +1946,89 @@
       <c r="P18" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="Q18" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R18" s="3">
         <v>-2276100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-510100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-772600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>3102000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-2084700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>2159500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>640100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>465500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>-671300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>507500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>330500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>1397500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>81700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-258500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-544700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>551400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>228300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-104100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-246000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>454600</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>-123400</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>-33700</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>1666200</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>724200</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>-6443000</v>
       </c>
-      <c r="AP18" s="3">
+      <c r="AQ18" s="3">
         <v>-126800</v>
       </c>
     </row>
-    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2039,8 +2071,9 @@
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
       <c r="AP19" s="3"/>
+      <c r="AQ19" s="3"/>
     </row>
-    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
@@ -2083,86 +2116,89 @@
       <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="Q20" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R20" s="3">
         <v>679000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>699200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>732300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-26000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>88900</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>30400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>384100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>291000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>54900</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>52900</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>244400</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-184400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-573200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>105300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>11800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>52600</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-67400</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>33200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-19800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-16500</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-124500</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>123400</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>563200</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>200700</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-628000</v>
       </c>
-      <c r="AP20" s="3">
+      <c r="AQ20" s="3">
         <v>5900</v>
       </c>
     </row>
-    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
@@ -2205,86 +2241,89 @@
       <c r="P21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="Q21" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R21" s="3">
         <v>-1457600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>470100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>-294900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>3542500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>-1599000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>2623500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>2076900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>1133100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>1485100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>966300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>986200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>1544700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>1438200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>568400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-230600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>909100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>436500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>194900</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>36200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>668700</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>136900</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>342200</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>2539100</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>1070500</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>-1513000</v>
       </c>
-      <c r="AP21" s="3">
+      <c r="AQ21" s="3">
         <v>571600</v>
       </c>
     </row>
-    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -2327,86 +2366,89 @@
       <c r="P22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="Q22" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R22" s="3">
         <v>482900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>171800</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>125100</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>115000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>104100</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>90000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>77200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>93100</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>64800</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>65400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>89500</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>93800</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>89900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>75900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>78800</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>62200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>53200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>50900</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>50500</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>47200</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>56100</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>120100</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>218800</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>265300</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>198400</v>
       </c>
-      <c r="AP22" s="3">
+      <c r="AQ22" s="3">
         <v>270000</v>
       </c>
     </row>
-    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
@@ -2449,86 +2491,89 @@
       <c r="P23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="Q23" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R23" s="3">
         <v>-2080100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>17300</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-165400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>2961000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-2099900</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>2099900</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>946900</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>663400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-681200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>495100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>485500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>1119300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-581400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-229100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-611700</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>541900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>107600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-121800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-316200</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>390900</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>-304100</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>-30300</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>2010600</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>659700</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>-7269400</v>
       </c>
-      <c r="AP23" s="3">
+      <c r="AQ23" s="3">
         <v>-390900</v>
       </c>
     </row>
-    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
@@ -2571,86 +2616,89 @@
       <c r="P24" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="Q24" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R24" s="3">
         <v>-2886400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-60500</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-97900</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>515400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>62900</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>573500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>408400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-299400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-147600</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>55000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>172400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>341500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>120200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-53900</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-269400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>93300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>127800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>-100800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>27500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>67000</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>56100</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>-53900</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>301800</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>72800</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>-529400</v>
       </c>
-      <c r="AP24" s="3">
+      <c r="AQ24" s="3">
         <v>84500</v>
       </c>
     </row>
-    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2771,8 +2819,11 @@
       <c r="AP25" s="3">
         <v>0</v>
       </c>
+      <c r="AQ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
@@ -2815,86 +2866,89 @@
       <c r="P26" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="Q26" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R26" s="3">
         <v>806300</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>77800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-67500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>2445600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-2162800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>1526400</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>538500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>962800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-533600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>440100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>313100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>777800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-701600</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-175200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-342300</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>448600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>-20100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-21000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-343700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>323900</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>-360200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>23600</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>1708800</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>586900</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>-6740000</v>
       </c>
-      <c r="AP26" s="3">
+      <c r="AQ26" s="3">
         <v>-475400</v>
       </c>
     </row>
-    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
@@ -2937,86 +2991,89 @@
       <c r="P27" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="Q27" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R27" s="3">
         <v>681200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>20500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-90300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>2350100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-2262500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>1491700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>568100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>946900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-544600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>428700</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>301100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>749500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-721500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-268300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-504700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-62200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>-397500</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-87500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-379900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>-34000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>-561000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>85300</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>1761500</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>190200</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>-6715400</v>
       </c>
-      <c r="AP27" s="3">
+      <c r="AQ27" s="3">
         <v>-523500</v>
       </c>
     </row>
-    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3137,8 +3194,11 @@
       <c r="AP28" s="3">
         <v>0</v>
       </c>
+      <c r="AQ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3181,8 +3241,8 @@
       <c r="P29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q29" s="3">
-        <v>0</v>
+      <c r="Q29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R29" s="3">
         <v>0</v>
@@ -3190,8 +3250,8 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
@@ -3202,65 +3262,68 @@
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
+      <c r="X29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y29" s="3">
         <v>0</v>
       </c>
       <c r="Z29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA29" s="3">
         <v>177500</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>21800</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>32700</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>29200</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>10387900</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>350600</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>1211800</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>870600</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AI29" s="3">
         <v>-163900</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>-123000</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>714800</v>
       </c>
-      <c r="AK29" s="3">
+      <c r="AL29" s="3">
         <v>203100</v>
       </c>
-      <c r="AL29" s="3">
+      <c r="AM29" s="3">
         <v>-590200</v>
       </c>
-      <c r="AM29" s="3">
+      <c r="AN29" s="3">
         <v>171700</v>
       </c>
-      <c r="AN29" s="3">
+      <c r="AO29" s="3">
         <v>920300</v>
       </c>
-      <c r="AO29" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AP29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AQ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3381,8 +3444,11 @@
       <c r="AP30" s="3">
         <v>0</v>
       </c>
+      <c r="AQ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3503,8 +3569,11 @@
       <c r="AP31" s="3">
         <v>0</v>
       </c>
+      <c r="AQ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
@@ -3547,86 +3616,89 @@
       <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="Q32" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R32" s="3">
         <v>-679000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-699200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-732300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>26000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-88900</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-30400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-384100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-291000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-54900</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-52900</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-244400</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>184400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>573200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-105300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-11800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-52600</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>67400</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-33200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>19800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>16500</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>124500</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-123400</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-563200</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-200700</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>628000</v>
       </c>
-      <c r="AP32" s="3">
+      <c r="AQ32" s="3">
         <v>-5900</v>
       </c>
     </row>
-    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
@@ -3669,86 +3741,89 @@
       <c r="P33" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="Q33" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R33" s="3">
         <v>681200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>20500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-90300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>2350100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-2262500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>1491700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>568100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>946900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-544600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>606100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>322900</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>782200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-692300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>10119600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-154100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>1149500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>473200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-251400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-502900</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>680800</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>-357900</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>-504900</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>1933200</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>1110400</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>-6715400</v>
       </c>
-      <c r="AP33" s="3">
+      <c r="AQ33" s="3">
         <v>-523500</v>
       </c>
     </row>
-    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3869,8 +3944,11 @@
       <c r="AP34" s="3">
         <v>0</v>
       </c>
+      <c r="AQ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
@@ -3913,213 +3991,219 @@
       <c r="P35" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="Q35" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R35" s="3">
         <v>681200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>20500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-90300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>2350100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-2262500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>1491700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>568100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>946900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-544600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>606100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>322900</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>782200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-692300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>10119600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-154100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>1149500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>473200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-251400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-502900</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>680800</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>-357900</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>-504900</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>1933200</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>1110400</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>-6715400</v>
       </c>
-      <c r="AP35" s="3">
+      <c r="AQ35" s="3">
         <v>-523500</v>
       </c>
     </row>
-    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43465</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43373</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43190</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43100</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>43008</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42916</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42825</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42735</v>
       </c>
-      <c r="AP38" s="2">
+      <c r="AQ38" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4162,8 +4246,9 @@
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
       <c r="AP39" s="3"/>
+      <c r="AQ39" s="3"/>
     </row>
-    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4206,1106 +4291,1134 @@
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
       <c r="AP40" s="3"/>
+      <c r="AQ40" s="3"/>
     </row>
-    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>6975900</v>
+      </c>
+      <c r="E41" s="3">
         <v>7910800</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>9080700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>3583200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>3929500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>2985300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5269700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>5037900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5860900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>4191400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7645600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>8178500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>9304600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>7382700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>7739900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3573900</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5021600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6908200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6314900</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3876700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7451500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>6706700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4761600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4250200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>3688400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3482200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3726400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>6787700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3840900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>5244100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4167400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>5114900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>3571800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>4270100</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>4412800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>6093500</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>12234200</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>4338400</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>5371400</v>
       </c>
-      <c r="AP41" s="3">
+      <c r="AQ41" s="3">
         <v>3453300</v>
       </c>
     </row>
-    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3">
+        <v>7675100</v>
+      </c>
+      <c r="E42" s="3">
         <v>7026400</v>
       </c>
-      <c r="E42" s="3">
+      <c r="F42" s="3">
         <v>6592700</v>
       </c>
-      <c r="F42" s="3">
+      <c r="G42" s="3">
         <v>6859100</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>6959500</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>6245100</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>7092900</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>7087900</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>6222000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>7142100</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>8537600</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>7836600</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>8517500</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>9613200</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>14917200</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>4615700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>8715700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>8203700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>8716200</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>3800900</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>4224600</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>2979300</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>4208000</v>
       </c>
-      <c r="Z42" s="3">
+      <c r="AA42" s="3">
         <v>3782100</v>
       </c>
-      <c r="AA42" s="3">
+      <c r="AB42" s="3">
         <v>2514500</v>
       </c>
-      <c r="AB42" s="3">
+      <c r="AC42" s="3">
         <v>3554200</v>
       </c>
-      <c r="AC42" s="3">
+      <c r="AD42" s="3">
         <v>3803400</v>
       </c>
-      <c r="AD42" s="3">
+      <c r="AE42" s="3">
         <v>3735000</v>
       </c>
-      <c r="AE42" s="3">
+      <c r="AF42" s="3">
         <v>2816300</v>
       </c>
-      <c r="AF42" s="3">
+      <c r="AG42" s="3">
         <v>2589800</v>
       </c>
-      <c r="AG42" s="3">
+      <c r="AH42" s="3">
         <v>4269100</v>
       </c>
-      <c r="AH42" s="3">
+      <c r="AI42" s="3">
         <v>3179900</v>
       </c>
-      <c r="AI42" s="3">
+      <c r="AJ42" s="3">
         <v>3624500</v>
       </c>
-      <c r="AJ42" s="3">
+      <c r="AK42" s="3">
         <v>5669000</v>
       </c>
-      <c r="AK42" s="3">
+      <c r="AL42" s="3">
         <v>5489900</v>
       </c>
-      <c r="AL42" s="3">
+      <c r="AM42" s="3">
         <v>5192600</v>
       </c>
-      <c r="AM42" s="3">
+      <c r="AN42" s="3">
         <v>5685100</v>
       </c>
-      <c r="AN42" s="3">
+      <c r="AO42" s="3">
         <v>12002200</v>
       </c>
-      <c r="AO42" s="3">
+      <c r="AP42" s="3">
         <v>11532700</v>
       </c>
-      <c r="AP42" s="3">
+      <c r="AQ42" s="3">
         <v>8993700</v>
       </c>
     </row>
-    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>9748700</v>
+      </c>
+      <c r="E43" s="3">
         <v>10177600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>6982500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>7297900</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>8024700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>6734800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>8190300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>6114200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>5943400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>6891800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>9391000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>9131000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>9068800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>8622300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>20684400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>9542600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>6370800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>7947600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>20913400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>4862200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>3126400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>3448000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>5702100</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2352900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2581100</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>3950200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>7209900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3247400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1783400</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>2140000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>5732300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1710100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1536100</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>7641000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>8521500</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>4906500</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>5880300</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>7654400</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>7869200</v>
       </c>
-      <c r="AP43" s="3">
+      <c r="AQ43" s="3">
         <v>5332600</v>
       </c>
     </row>
-    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2217500</v>
+      </c>
+      <c r="E44" s="3">
         <v>1700700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1789400</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2150700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1694700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1302400</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2650400</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>3305800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2632600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2144800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2509100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2660900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2291500</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1973100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>4658600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>10575700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>8750500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>3071600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>3065800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>6031900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1794400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1055900</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1627800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1742600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1266500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1729100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1850300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1832600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1452900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1410300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1929300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2056800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1553700</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1437300</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>2158700</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>2521100</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>2024100</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1935600</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>2310100</v>
       </c>
-      <c r="AP44" s="3">
+      <c r="AQ44" s="3">
         <v>2759600</v>
       </c>
     </row>
-    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>20856800</v>
+      </c>
+      <c r="E45" s="3">
         <v>25769600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>15447900</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>11188500</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>14405200</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>14979500</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>12710400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>19958700</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>20641800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>30597700</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>27589300</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>32128500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>39467200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>48594100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>58619700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>162450800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>133916800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>124044800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>73135600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>97899700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>35390100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>16092200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>10853700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>10846100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>18832400</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>18091700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>16378800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>14982900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>64489100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>64420200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>56665600</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>60091700</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>52903800</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>9127700</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>5632400</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>7180700</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>8292600</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>9004300</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>8707300</v>
       </c>
-      <c r="AP45" s="3">
+      <c r="AQ45" s="3">
         <v>8604000</v>
       </c>
     </row>
-    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>47474000</v>
+      </c>
+      <c r="E46" s="3">
         <v>52585000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>40311100</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>31079400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>35013500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>32247100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>36258400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>41504600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>41300800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>50967700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>55964400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>59935400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>68649600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>76185400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>106619800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>190758700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>162775400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>150175900</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>112145800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>116471400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>51986900</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>30282100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>27153200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>22973900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>28882900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>30807300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>32968800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>30585600</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>74382600</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>75804400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>72763700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>72153500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>63189900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>28145000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>26215300</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>25894400</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>34116300</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>34934900</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>35790600</v>
       </c>
-      <c r="AP46" s="3">
+      <c r="AQ46" s="3">
         <v>29143400</v>
       </c>
     </row>
-    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>17574500</v>
+      </c>
+      <c r="E47" s="3">
         <v>16056700</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>14348900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>13970400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>13618300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>11974700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>10096300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>11667400</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>10683600</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>10890100</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>10542700</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>9870900</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>10262000</v>
       </c>
-      <c r="P47" s="3">
+      <c r="Q47" s="3">
         <v>10004300</v>
       </c>
-      <c r="Q47" s="3">
+      <c r="R47" s="3">
         <v>9327100</v>
       </c>
-      <c r="R47" s="3">
+      <c r="S47" s="3">
         <v>8367900</v>
       </c>
-      <c r="S47" s="3">
+      <c r="T47" s="3">
         <v>8330500</v>
       </c>
-      <c r="T47" s="3">
+      <c r="U47" s="3">
         <v>8536800</v>
       </c>
-      <c r="U47" s="3">
+      <c r="V47" s="3">
         <v>9585600</v>
       </c>
-      <c r="V47" s="3">
+      <c r="W47" s="3">
         <v>8504800</v>
       </c>
-      <c r="W47" s="3">
+      <c r="X47" s="3">
         <v>7900100</v>
       </c>
-      <c r="X47" s="3">
+      <c r="Y47" s="3">
         <v>8492600</v>
       </c>
-      <c r="Y47" s="3">
+      <c r="Z47" s="3">
         <v>7765800</v>
       </c>
-      <c r="Z47" s="3">
+      <c r="AA47" s="3">
         <v>7938900</v>
       </c>
-      <c r="AA47" s="3">
+      <c r="AB47" s="3">
         <v>8344400</v>
       </c>
-      <c r="AB47" s="3">
+      <c r="AC47" s="3">
         <v>8278900</v>
       </c>
-      <c r="AC47" s="3">
+      <c r="AD47" s="3">
         <v>9351000</v>
       </c>
-      <c r="AD47" s="3">
+      <c r="AE47" s="3">
         <v>9232700</v>
       </c>
-      <c r="AE47" s="3">
+      <c r="AF47" s="3">
         <v>2258700</v>
       </c>
-      <c r="AF47" s="3">
+      <c r="AG47" s="3">
         <v>2259600</v>
       </c>
-      <c r="AG47" s="3">
+      <c r="AH47" s="3">
         <v>2629600</v>
       </c>
-      <c r="AH47" s="3">
+      <c r="AI47" s="3">
         <v>2008100</v>
       </c>
-      <c r="AI47" s="3">
+      <c r="AJ47" s="3">
         <v>1944600</v>
       </c>
-      <c r="AJ47" s="3">
+      <c r="AK47" s="3">
         <v>4478700</v>
       </c>
-      <c r="AK47" s="3">
+      <c r="AL47" s="3">
         <v>5105100</v>
       </c>
-      <c r="AL47" s="3">
+      <c r="AM47" s="3">
         <v>4516000</v>
       </c>
-      <c r="AM47" s="3">
+      <c r="AN47" s="3">
         <v>4481200</v>
       </c>
-      <c r="AN47" s="3">
+      <c r="AO47" s="3">
         <v>4690500</v>
       </c>
-      <c r="AO47" s="3">
+      <c r="AP47" s="3">
         <v>5381900</v>
       </c>
-      <c r="AP47" s="3">
+      <c r="AQ47" s="3">
         <v>4327800</v>
       </c>
     </row>
-    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>52428900</v>
+      </c>
+      <c r="E48" s="3">
         <v>51199100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>48164800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>51148700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>49021700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>43933200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>38769000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>39408900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>35789100</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>33812700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>31283300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>29897300</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>29527300</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>30473700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>26304400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>26292400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>23396300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>21669600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>21664700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>21499900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>20445900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>20193000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>17855500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>19987900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>20822200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>20744700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>22199500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>23813800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>15313200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>15536200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>14678600</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>13499400</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>13162800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>27510400</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>27990300</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>27179100</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>27115100</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>29009500</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>28779500</v>
       </c>
-      <c r="AP48" s="3">
+      <c r="AQ48" s="3">
         <v>32883100</v>
       </c>
     </row>
-    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>9829800</v>
+      </c>
+      <c r="E49" s="3">
         <v>9980400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>10169100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>11023100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>11202600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>10809600</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>10591200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>11325000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>11143300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>11187800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>10791400</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>10599100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>10935600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>10470400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>6277900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>6195700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>6235900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>6311400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>6378800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>6331100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>6266500</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>5301600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>4886300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>4697500</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>5054200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>5211300</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>5576700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>5570000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>2563400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>2648400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>2594100</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>2426800</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>2328900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>13676700</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>13893600</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>13744400</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>14279600</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>14989600</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>14964900</v>
       </c>
-      <c r="AP49" s="3">
+      <c r="AQ49" s="3">
         <v>14848700</v>
       </c>
     </row>
-    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5426,8 +5539,11 @@
       <c r="AP50" s="3">
         <v>0</v>
       </c>
+      <c r="AQ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5548,130 +5664,136 @@
       <c r="AP51" s="3">
         <v>0</v>
       </c>
+      <c r="AQ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>4677300</v>
+      </c>
+      <c r="E52" s="3">
         <v>4546300</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>6006800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>5474600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>5821500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>4752500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>5839100</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>5304500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>4985500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>3864500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>8312100</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>4363900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>4703100</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>4567600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>4926600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>7131500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5575400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4908500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4502300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>5062700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4630900</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4403400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3821000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>4392400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>4749800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>4743300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>4628800</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2459800</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2530400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2464200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2093700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>2389100</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>2775700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>4765300</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>4279300</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>4656300</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>4650600</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>5197600</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>4764500</v>
       </c>
-      <c r="AP52" s="3">
+      <c r="AQ52" s="3">
         <v>5808000</v>
       </c>
     </row>
-    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5792,130 +5914,136 @@
       <c r="AP53" s="3">
         <v>0</v>
       </c>
+      <c r="AQ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>132216400</v>
+      </c>
+      <c r="E54" s="3">
         <v>134630500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>119428200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>112875700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>114864400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>103888900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>101917400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>109938700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>104552700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>111405800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>117731800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>115208500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>124690000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>132397900</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>153455800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>238746100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>206313600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>191602300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>154277200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>157869900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>91230300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>68672700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>61481700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>59990600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>67853500</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>69785500</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>74724700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>71661900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>97048300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>98712800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>94759800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>92476800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>83401900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>78576200</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>77483500</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>75990100</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>84642900</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>88822200</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>89681400</v>
       </c>
-      <c r="AP54" s="3">
+      <c r="AQ54" s="3">
         <v>87011000</v>
       </c>
     </row>
-    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5958,8 +6086,9 @@
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
       <c r="AP55" s="3"/>
+      <c r="AQ55" s="3"/>
     </row>
-    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -6002,740 +6131,759 @@
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
       <c r="AP56" s="3"/>
+      <c r="AQ56" s="3"/>
     </row>
-    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>6706300</v>
+      </c>
+      <c r="E57" s="3">
         <v>6935300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>7048300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>5340800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>5325900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>5656100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>5672400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>5196300</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>4405900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>4993000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>5652700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>7894800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>7491300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>6537400</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>8267100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>7865300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>6189100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>6355900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>4800400</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>4009000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>2752900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>2818500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>2380800</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>2020800</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>2294200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>3258500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>3487100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>2926500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>2709200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>3045500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>2873300</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>2291600</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>2299200</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>5138600</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>5696300</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>4651800</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>4757200</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>5730500</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>6375000</v>
       </c>
-      <c r="AP57" s="3">
+      <c r="AQ57" s="3">
         <v>5558000</v>
       </c>
     </row>
-    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>8646200</v>
+      </c>
+      <c r="E58" s="3">
         <v>9348600</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>4905500</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>5037000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>6078700</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>6281900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>4035600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>4654200</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>2629400</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>2870900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>3276200</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>6195000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>7791500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>8287700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>12420600</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>17656500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>10748300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>11692000</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>11920800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>7271100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1488600</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1352100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1243800</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1479000</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>2400000</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1842500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>4084800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>5059200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>2574000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>4241700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>906100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1031200</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>729100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>3687100</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>3127000</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>5084900</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>3852900</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>4299700</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>2514300</v>
       </c>
-      <c r="AP58" s="3">
+      <c r="AQ58" s="3">
         <v>3786700</v>
       </c>
     </row>
-    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>19857200</v>
+      </c>
+      <c r="E59" s="3">
         <v>25503300</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>13947400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>13441300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>16122100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>14771900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>17867300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>17012000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>16720200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>24784800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>26287200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>27633400</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>34232500</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>42772700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>67571400</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>179801500</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>147926100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>132240900</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>88444100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>100529700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>35675800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>15435200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>12833500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>9764600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>15458200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>16334200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>17428300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>15165400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>54054400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>53331400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>50449500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>51325100</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>46528800</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>13774400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>13946300</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>13215900</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>21579200</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>22555900</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>24876600</v>
       </c>
-      <c r="AP59" s="3">
+      <c r="AQ59" s="3">
         <v>15245400</v>
       </c>
     </row>
-    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>35209600</v>
+      </c>
+      <c r="E60" s="3">
         <v>41787200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>26921500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>23819100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>27526700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>26709900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>28548500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>26862600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>23755500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>32648600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>36579000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>41723100</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>49515300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>57597800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>88259100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>205323300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>164863500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>150288800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>105165300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>111809700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>39917300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>19605800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>16458100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>13264400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>20152400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>21435300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>22887100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>23151100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>59337600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>60618600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>54228900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>54647900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>49557100</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>22600100</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>22769700</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>22952500</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>30189400</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>32586100</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>33765800</v>
       </c>
-      <c r="AP60" s="3">
+      <c r="AQ60" s="3">
         <v>24590100</v>
       </c>
     </row>
-    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>18746700</v>
+      </c>
+      <c r="E61" s="3">
         <v>18939200</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>18209500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>18348000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>17709900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>15420400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>15293500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>17754900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>17488500</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>15780600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>15545500</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>13646300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>13954100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>13996100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>10842300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>11225200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>9947400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>7585200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>7369700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5652500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>5259300</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>4606500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>3940700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>3834000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>4528400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>4280700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>4580900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>4568000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>2979800</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>2892400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>2363400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>2158700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1731500</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>15890300</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>16172400</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>15289400</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>17165300</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>18529800</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>18829100</v>
       </c>
-      <c r="AP61" s="3">
+      <c r="AQ61" s="3">
         <v>18809100</v>
       </c>
     </row>
-    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>21197300</v>
+      </c>
+      <c r="E62" s="3">
         <v>22068500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>21176500</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>23079900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>23388100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>19965400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>18831100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>21138700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>21442200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>20871700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>21535300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>19039000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>20648500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>20982200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>21924900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>21978200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>21198400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>21470000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>23316800</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>22348700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>23612400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>23085600</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>23422900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>24121800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>25149800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>25394200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>26865600</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>24303800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>20443500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>20194200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>21302800</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>18493600</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>18421100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>24908100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>25087700</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>25078700</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>25138200</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>26906100</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>27707800</v>
       </c>
-      <c r="AP62" s="3">
+      <c r="AQ62" s="3">
         <v>35321100</v>
       </c>
     </row>
-    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6856,8 +7004,11 @@
       <c r="AP63" s="3">
         <v>0</v>
       </c>
+      <c r="AQ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6978,8 +7129,11 @@
       <c r="AP64" s="3">
         <v>0</v>
       </c>
+      <c r="AQ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -7100,130 +7254,136 @@
       <c r="AP65" s="3">
         <v>0</v>
       </c>
+      <c r="AQ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>77828200</v>
+      </c>
+      <c r="E66" s="3">
         <v>85257700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>70627000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>68678900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>71927200</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>65252900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>67107400</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>70737200</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>67871000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>74640200</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>80588000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>77539200</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>87444300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>95726900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>122912600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>240355200</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>197856800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>181256800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>137740300</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>141786200</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>70732600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>48185600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>44609700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>41456800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>50319300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>51657900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>54920800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>52583900</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>88114700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>89793900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>84425900</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>81244700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>75294300</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>69468300</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>69900000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>68985600</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>78183600</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>84445100</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>86448800</v>
       </c>
-      <c r="AP66" s="3">
+      <c r="AQ66" s="3">
         <v>82190200</v>
       </c>
     </row>
-    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7266,8 +7426,9 @@
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
       <c r="AP67" s="3"/>
+      <c r="AQ67" s="3"/>
     </row>
-    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7388,8 +7549,11 @@
       <c r="AP68" s="3">
         <v>0</v>
       </c>
+      <c r="AQ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7510,8 +7674,11 @@
       <c r="AP69" s="3">
         <v>0</v>
       </c>
+      <c r="AQ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7632,8 +7799,11 @@
       <c r="AP70" s="3">
         <v>0</v>
       </c>
+      <c r="AQ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7754,52 +7924,55 @@
       <c r="AP71" s="3">
         <v>0</v>
       </c>
+      <c r="AQ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E72" s="3">
+      <c r="E72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F72" s="3">
         <v>27207900</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="G72" s="3">
+      <c r="G72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H72" s="3">
         <v>25065200</v>
       </c>
-      <c r="H72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I72" s="3">
+      <c r="I72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J72" s="3">
         <v>19473000</v>
       </c>
-      <c r="J72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="K72" s="3">
+      <c r="K72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L72" s="3">
         <v>19211400</v>
       </c>
-      <c r="L72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="M72" s="3">
+      <c r="M72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N72" s="3">
         <v>16460700</v>
       </c>
-      <c r="N72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="O72" s="3">
+      <c r="O72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P72" s="3">
         <v>16886500</v>
       </c>
-      <c r="P72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q72" s="3">
-        <v>0</v>
+      <c r="Q72" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R72" s="3">
         <v>0</v>
@@ -7816,68 +7989,71 @@
       <c r="V72" s="3">
         <v>0</v>
       </c>
-      <c r="W72" s="3" t="s">
-        <v>8</v>
+      <c r="W72" s="3">
+        <v>0</v>
       </c>
       <c r="X72" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Y72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z72" s="3">
         <v>8572700</v>
       </c>
-      <c r="Z72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA72" s="3">
+      <c r="AA72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB72" s="3">
         <v>9936000</v>
       </c>
-      <c r="AB72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AC72" s="3">
+      <c r="AC72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD72" s="3">
         <v>10399300</v>
       </c>
-      <c r="AD72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AE72" s="3">
+      <c r="AE72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF72" s="3">
         <v>1345800</v>
       </c>
-      <c r="AF72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AG72" s="3">
+      <c r="AG72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH72" s="3">
         <v>1347300</v>
       </c>
-      <c r="AH72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AI72" s="3">
+      <c r="AI72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ72" s="3">
         <v>1371400</v>
       </c>
-      <c r="AJ72" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AK72" s="3">
+      <c r="AK72" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AL72" s="3">
         <v>2655800</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>2728700</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>3031600</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>932000</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>-765300</v>
       </c>
-      <c r="AP72" s="3">
+      <c r="AQ72" s="3">
         <v>2308900</v>
       </c>
     </row>
-    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7998,8 +8174,11 @@
       <c r="AP73" s="3">
         <v>0</v>
       </c>
+      <c r="AQ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -8120,8 +8299,11 @@
       <c r="AP74" s="3">
         <v>0</v>
       </c>
+      <c r="AQ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8242,130 +8424,136 @@
       <c r="AP75" s="3">
         <v>0</v>
       </c>
+      <c r="AQ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>45264500</v>
+      </c>
+      <c r="E76" s="3">
         <v>40682600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>40367500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>39897900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>38818600</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>36165200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>32662800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>36967400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>34581600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>34683400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>35407300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>35976900</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>35427900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>34862000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>30543200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-1609200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8456700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>10345500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>16536900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>16083700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>20497700</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>20487100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>16872000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>18533800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>17534200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>18127700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>19803900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>19078000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>8933600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>8918900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>10333800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>11232200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>8107600</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>9107900</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>7583500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>7004600</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>6459300</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>4377100</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>3232700</v>
       </c>
-      <c r="AP76" s="3">
+      <c r="AQ76" s="3">
         <v>4820800</v>
       </c>
     </row>
-    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8486,135 +8674,141 @@
       <c r="AP77" s="3">
         <v>0</v>
       </c>
+      <c r="AQ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:43" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:43" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43465</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43373</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43281</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43190</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43100</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>43008</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42916</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42825</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42735</v>
       </c>
-      <c r="AP80" s="2">
+      <c r="AQ80" s="2">
         <v>42643</v>
       </c>
     </row>
-    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
@@ -8657,86 +8851,89 @@
       <c r="P81" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="Q81" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R81" s="3">
         <v>681200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>20500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-90300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>2350100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-2262500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>1491700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>568100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>946900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-544600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>606100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>322900</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>782200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-692300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>10119600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-154100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>1149500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>473200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-251400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-502900</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>680800</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>-357900</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>-504900</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>1933200</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>1110400</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>-6715400</v>
       </c>
-      <c r="AP81" s="3">
+      <c r="AQ81" s="3">
         <v>-523500</v>
       </c>
     </row>
-    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8779,130 +8976,134 @@
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
       <c r="AP82" s="3"/>
+      <c r="AQ82" s="3"/>
     </row>
-    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>624800</v>
+      </c>
+      <c r="E83" s="3">
         <v>514500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>84900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>527500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>1070400</v>
       </c>
-      <c r="H83" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I83" s="3">
+      <c r="I83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J83" s="3">
         <v>-706300</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>516500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>1714000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>545400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>3283100</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>-1798400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>-244600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>477700</v>
       </c>
-      <c r="Q83" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="R83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S83" s="3">
+      <c r="S83" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="T83" s="3">
         <v>-254600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>466600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>396800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>433600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>1052700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>376600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>2101500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>405800</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>411300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>331600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>1929700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>721500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>302300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>305000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>275600</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>265800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>9900</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>522600</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>741600</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>1098400</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>918900</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>145600</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>5558000</v>
       </c>
-      <c r="AP83" s="3">
+      <c r="AQ83" s="3">
         <v>692500</v>
       </c>
     </row>
-    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -9023,8 +9224,11 @@
       <c r="AP84" s="3">
         <v>0</v>
       </c>
+      <c r="AQ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -9145,8 +9349,11 @@
       <c r="AP85" s="3">
         <v>0</v>
       </c>
+      <c r="AQ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9267,8 +9474,11 @@
       <c r="AP86" s="3">
         <v>0</v>
       </c>
+      <c r="AQ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9389,8 +9599,11 @@
       <c r="AP87" s="3">
         <v>0</v>
       </c>
+      <c r="AQ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9511,130 +9724,136 @@
       <c r="AP88" s="3">
         <v>0</v>
       </c>
+      <c r="AQ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>1701100</v>
+      </c>
+      <c r="E89" s="3">
         <v>-1796400</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>4660100</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>2632900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>946600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>-2231900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>5072000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>1409800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>2792200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-2318500</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>1239100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>1156900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>1226000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>962600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1276000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-1784200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>236100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>2916500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>4177000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>-1724800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>3614100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>1688600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>2350900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>657000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>2616000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>-1323300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>572000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-378500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>1589300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-3654400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2073600</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>3429100</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>1575600</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>399700</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>1298100</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-5189200</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>3194300</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>-1329900</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>2047100</v>
       </c>
-      <c r="AP89" s="3">
+      <c r="AQ89" s="3">
         <v>1892200</v>
       </c>
     </row>
-    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9677,53 +9896,54 @@
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
       <c r="AP90" s="3"/>
+      <c r="AQ90" s="3"/>
     </row>
-    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-3165800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-2984000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-2836700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-2752600</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-2805600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-3094500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-3259100</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-2782700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-2154700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-1858900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-1958700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-1580200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-1099300</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-949600</v>
       </c>
-      <c r="Q91" s="3">
-        <v>0</v>
-      </c>
       <c r="R91" s="3">
         <v>0</v>
       </c>
@@ -9748,59 +9968,62 @@
       <c r="Y91" s="3">
         <v>0</v>
       </c>
-      <c r="Z91" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="AA91" s="3">
+      <c r="Z91" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB91" s="3">
         <v>-488700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-645800</v>
       </c>
-      <c r="AC91" s="3" t="s">
-        <v>8</v>
-      </c>
       <c r="AD91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AE91" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-430600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-232100</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>764200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-500600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-417200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-11000</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>336600</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-232300</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>52700</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-419100</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-1203200</v>
       </c>
-      <c r="AP91" s="3">
+      <c r="AQ91" s="3">
         <v>-611600</v>
       </c>
     </row>
-    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9921,8 +10144,11 @@
       <c r="AP92" s="3">
         <v>0</v>
       </c>
+      <c r="AQ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -10043,130 +10269,136 @@
       <c r="AP93" s="3">
         <v>0</v>
       </c>
+      <c r="AQ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-5804900</v>
+      </c>
+      <c r="E94" s="3">
         <v>-3484400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-2768600</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-2702100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-2998200</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-2029800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-3858600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-3318100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-1525800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-1711100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-1234700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-985400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-1100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-813800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-11479200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>2785000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2144600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-145400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-5737100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-125800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2243000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-222200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2310000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1994800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-703600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>577100</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-616400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1836300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-645800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>2209400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1895000</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-995700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-1183600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-905900</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-1836700</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>31400</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>5607700</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-819300</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-4265600</v>
       </c>
-      <c r="AP94" s="3">
+      <c r="AQ94" s="3">
         <v>-120900</v>
       </c>
     </row>
-    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -10209,52 +10441,53 @@
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
       <c r="AP95" s="3"/>
+      <c r="AQ95" s="3"/>
     </row>
-    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>870600</v>
+      </c>
+      <c r="E96" s="3">
         <v>100300</v>
       </c>
-      <c r="E96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="F96" s="3">
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3">
         <v>207700</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>863200</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>80000</v>
       </c>
-      <c r="I96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J96" s="3">
+      <c r="J96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K96" s="3">
         <v>246500</v>
       </c>
-      <c r="K96" s="3">
+      <c r="L96" s="3">
         <v>676100</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>121900</v>
       </c>
-      <c r="M96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="N96" s="3">
+      <c r="N96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="O96" s="3">
         <v>230700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>730300</v>
       </c>
-      <c r="P96" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>0</v>
+      <c r="Q96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R96" s="3">
         <v>0</v>
@@ -10331,8 +10564,11 @@
       <c r="AP96" s="3">
         <v>0</v>
       </c>
+      <c r="AQ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10453,8 +10689,11 @@
       <c r="AP97" s="3">
         <v>0</v>
       </c>
+      <c r="AQ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10575,8 +10814,11 @@
       <c r="AP98" s="3">
         <v>0</v>
       </c>
+      <c r="AQ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10697,370 +10939,382 @@
       <c r="AP99" s="3">
         <v>0</v>
       </c>
+      <c r="AQ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>3179500</v>
+      </c>
+      <c r="E100" s="3">
         <v>4312200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>3638600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-55100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>2857300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>1757500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-654300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>785200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>420000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>703400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-882100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-1029800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>664800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-429200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>14305800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-2477000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-20700</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-2159200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>3965600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-1889600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-636900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>152400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>647300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>2013500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-1196700</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>308700</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-1862000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>3279300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2746900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>1766800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-1030300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-399800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-141600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>407400</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-1132100</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-976100</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-669800</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>1103400</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>4138900</v>
       </c>
-      <c r="AP100" s="3">
+      <c r="AQ100" s="3">
         <v>-1479000</v>
       </c>
     </row>
-    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-119800</v>
+      </c>
+      <c r="E101" s="3">
         <v>-11900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>34200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>60200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>11800</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>55000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-17700</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>5300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>7600</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>70600</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-24600</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>56900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>10500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-12200</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-25500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>62700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>10900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-11900</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>14100</v>
       </c>
-      <c r="V101" s="3">
-        <v>0</v>
-      </c>
       <c r="W101" s="3">
+        <v>0</v>
+      </c>
+      <c r="X101" s="3">
         <v>10600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>37000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-11000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>59200</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-76400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-10900</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-819500</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>868500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-8200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>17900</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-1200</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-10000</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>2200</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>23100</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>-28000</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>-2200</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>-3400</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>12900</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>-2300</v>
       </c>
-      <c r="AP101" s="3">
+      <c r="AQ101" s="3">
         <v>-1200</v>
       </c>
     </row>
-    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:43" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-891100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-961600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>5494900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-342600</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>685800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2516200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>593200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-1062900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1698300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-3271100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-895300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-853100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1897400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-209700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>4077100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1413600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1918300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>600000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2419700</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-3740100</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>744800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1655800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>677200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>734800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>639300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-448400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2725900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1933000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1811700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>339700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-852900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>2023600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>252500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-75800</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-1697600</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-6137300</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>8128800</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-1033000</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>1918000</v>
       </c>
-      <c r="AP102" s="3">
+      <c r="AQ102" s="3">
         <v>291100</v>
       </c>
     </row>
